--- a/project/Template19.xlsx
+++ b/project/Template19.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\Tanda Terima Versi Website\Sample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\Desktop\Rev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C76D54-1A5B-4A22-9478-739BC751AC5B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA3993A-BA62-4535-B11F-24256E5608B9}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,7 @@
     <t>Novia Auni Azalia</t>
   </si>
   <si>
-    <t>Jl. Margonda Raya No.518G, Pondok Cina, Beji, Kota Depok</t>
+    <t>Jl. Margonda Raya No.514F, Pondok Cina, Beji, Kota Depok</t>
   </si>
 </sst>
 </file>
@@ -469,10 +469,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2520,21 +2520,21 @@
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
       <c r="D47" s="10"/>
-      <c r="K47" s="47" t="s">
+      <c r="K47" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="L47" s="47"/>
-      <c r="M47" s="47"/>
-      <c r="N47" s="47"/>
-      <c r="O47" s="47"/>
+      <c r="L47" s="46"/>
+      <c r="M47" s="46"/>
+      <c r="N47" s="46"/>
+      <c r="O47" s="46"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A49" s="16"/>
